--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_923_Iran_Sea_of_Oman.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_923_Iran_Sea_of_Oman.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R479fc43dc81f4ee1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Ra8773929cc8e40d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R73a5aeaeabfe47b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Re24550e0fedf4c48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R4c621dc283d245dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R2ba3ec27a9c24bdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R6b623730b29c4c86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R53491f4264514bff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rff5c77f7c05f40b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Ra4a6e88623da4ff4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R3982b3aff2ed436d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R4efc1d25e8d84254"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ923CommercialTable" displayName="EEZ923CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ923CommercialTable" displayName="EEZ923CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ923FunctionalTable" displayName="EEZ923FunctionalTable" ref="A1:O22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O22"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ923FunctionalTable" displayName="EEZ923FunctionalTable" ref="A1:E22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E22"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ923ValidationTable" displayName="EEZ923ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ923ValidationTable" displayName="EEZ923ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -10878,7 +10832,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6823c1ee9b6480e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R218943d33833427d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10888,20 +10842,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -10909,606 +10853,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>19.1130180743</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.34</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>218.77616239495518</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>19.1130180743</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>218.77616239495518</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$153,A2,'Species'!$U$2:$U$153))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>4181.472746080771</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.34</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>218.77616239495518</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>4181.472746080771</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>8088.1982518553</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.8001110735001506</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>63.11187363615465</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>8088.1982518553</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>111.55576293244312</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$153,A3,'Species'!$U$2:$U$153))</x:f>
-        <x:v>902285.1267345707</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.8001110735001506</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>63.11187363615465</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>510461.34601525863</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>391823.7807193121</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.7675875632463653</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.7675875632463652</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>2468.9442106813003</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.308735103275783</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2035.7999683447206</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>2468.9442106813003</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2303.093839271421</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$153,A4,'Species'!$U$2:$U$153))</x:f>
-        <x:v>5686210.201124945</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.308735103275783</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2035.7999683447206</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>5026276.545949873</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>659933.6551750721</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.131296726143499</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.13129672614349894</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>68411.8890072198</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.49353776219222</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>31.15571785222345</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>68411.8890072198</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>87.78026528926286</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$153,A5,'Species'!$U$2:$U$153))</x:f>
-        <x:v>6005213.7659933595</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.49353776219222</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>31.15571785222345</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2131421.511646567</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>3873792.2543467926</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>2.8174688737912796</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>1.8174688737912796</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>33.517742475700004</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.06</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>114.81536214968828</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>33.517742475700004</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>114.81536214968828</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$153,A6,'Species'!$U$2:$U$153))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>3848.3517407874856</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.06</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>114.81536214968828</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>3848.3517407874856</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>79873.68630968791</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.375538232089072</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>237.4314430698722</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>79873.68630968791</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>305.1371486836687</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$153,A7,'Species'!$U$2:$U$153))</x:f>
-        <x:v>24372428.895391956</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.375538232089072</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>237.4314430698722</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>18964524.603819493</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>5407904.291572463</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.2851589694203724</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.2851589694203724</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>110189.37507259051</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.085924963967433</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1218.779003935244</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>110189.37507259051</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1874.2593477325195</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$153,A8,'Species'!$U$2:$U$153))</x:f>
-        <x:v>206523466.25060743</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.085924963967433</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1218.779003935244</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>134296496.79521886</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>72226969.45538858</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.5378172266512908</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.5378172266512908</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1580.7260204022002</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.63876700270292</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>435.27828592760545</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1580.7260204022002</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>445.9138837560902</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$153,A9,'Species'!$U$2:$U$153))</x:f>
-        <x:v>704867.6789118537</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.63876700270292</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>435.27828592760545</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>688055.7126818348</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>16811.96623001888</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.024434018815847</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.024434018815846868</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>8970.812182504498</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.9601851817141607</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>912.3998006467017</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>8970.812182504498</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1112.534340200596</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$153,A10,'Species'!$U$2:$U$153))</x:f>
-        <x:v>9980336.612526111</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.9601851817141607</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>912.3998006467017</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>8184967.246956107</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1795369.365570004</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.2193496090332776</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.21934960903327755</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>87830.5952754313</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.4430768859409175</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2773.811126781731</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>87830.5952754313</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2787.0420661041544</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$153,A11,'Species'!$U$2:$U$153))</x:f>
-        <x:v>244787563.72359586</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.4430768859409175</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2773.811126781731</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>243625482.4468543</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1162081.2767415643</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0047699496172164</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.004769949617216527</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf362a587940b4c1c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0f202371b784f7f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11518,20 +11068,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -11539,1200 +11079,421 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1487.3478860662</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.6914873259021723</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>491.45903764814176</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1487.3478860662</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>491.93579191106653</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$153,A2,'Species'!$U$2:$U$153))</x:f>
-        <x:v>731679.6601792269</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.6914873259021723</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>491.45903764814176</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>730970.5607340927</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>709.0994451341685</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0009700793482326</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0009700793482326297</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>8.989036059</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>31.622776601683793</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>8.989036059</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>31.622776601683793</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$153,A3,'Species'!$U$2:$U$153))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>284.2582791582371</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.5</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>31.622776601683793</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>284.2582791582371</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>19911.0061336484</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.317077770326046</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2075.285111284787</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>19911.0061336484</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2517.4569125286093</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$153,A4,'Species'!$U$2:$U$153))</x:f>
-        <x:v>50125100.0265527</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.317077770326046</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2075.285111284787</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>41321014.5798606</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>8804085.446692102</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.213065568118531</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.21306556811853103</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>3969.7099566659003</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.647680080144656</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>444.3038537045248</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>3969.7099566659003</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>523.8800873633246</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$153,A5,'Species'!$U$2:$U$153))</x:f>
-        <x:v>2079651.9989051912</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.647680080144656</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>444.3038537045248</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1763757.4318358817</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>315894.56706930953</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.179103181292054</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.17910318129205402</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>113457.01989174771</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.432972126499376</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2710.017694373464</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>113457.01989174771</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2755.9479988132057</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$153,A6,'Species'!$U$2:$U$153))</x:f>
-        <x:v>312681646.92197216</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.432972126499376</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2710.017694373464</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>307470531.4575184</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>5211115.464453757</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0169483411621636</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.016948341162163535</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>2223.3214494502</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.534114820167183</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>342.0698680878525</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>2223.3214494502</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>446.6086339235897</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$153,A7,'Species'!$U$2:$U$153))</x:f>
-        <x:v>992954.5553119691</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.534114820167183</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>342.0698680878525</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>760531.2749303229</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>232423.28038164624</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.3056064727948762</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.3056064727948762</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>22856.4413874934</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.350289712570201</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2240.215060462283</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>22856.4413874934</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2398.74759800073</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$153,A8,'Species'!$U$2:$U$153))</x:f>
-        <x:v>54826833.87709426</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.350289712570201</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2240.215060462283</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>51203344.224836156</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>3623489.6522581056</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0707666600124242</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.07076666001242422</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>6590.253227391</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.105362416737008</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1274.5662569952224</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>6590.253227391</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1344.7865447830009</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$153,A9,'Species'!$U$2:$U$153))</x:f>
-        <x:v>8862483.866908163</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.105362416737008</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1274.5662569952224</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>8399714.388686432</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>462769.47822173126</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0550934778026542</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.05509347780265423</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>2956.0225445263</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>2.5421660689785655</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>34.84705404996512</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>2956.0225445263</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>48.3083080837375</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$153,A10,'Species'!$U$2:$U$153))</x:f>
-        <x:v>142800.44778345016</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>2.5421660689785655</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>34.84705404996512</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>103008.6773820234</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>39791.770401426766</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.3862953239740465</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.38629532397404653</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>10115.2299604825</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.216584591992822</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>164.65866576751367</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>10115.2299604825</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>213.0016109784312</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$153,A11,'Species'!$U$2:$U$153))</x:f>
-        <x:v>2154560.2770000654</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.216584591992822</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>164.65866576751367</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1665560.2692246286</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>489000.00777543685</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.2935949042559005</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.2935949042559006</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>32984.5849474965</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.4724602835873046</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>296.79753084640356</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>32984.5849474965</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>446.19972651613153</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$153,A12,'Species'!$U$2:$U$153))</x:f>
-        <x:v>14717712.782821046</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.4724602835873046</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>296.79753084640356</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>9789743.36841041</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>4927969.414410636</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.5033808577977876</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.5033808577977877</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>55164.523641114596</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.4966195411655283</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>313.7758691011195</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>55164.523641114596</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>536.0157487673513</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$153,A13,'Species'!$U$2:$U$153))</x:f>
-        <x:v>29569053.444886293</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.4966195411655283</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>313.7758691011195</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>17309296.349039987</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>12259757.095846307</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.7082758795406643</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.7082758795406643</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>12809.912156527698</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.5444122324528045</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>350.2774927830222</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>12809.912156527698</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>739.2955562880978</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$153,A14,'Species'!$U$2:$U$153))</x:f>
-        <x:v>9470311.133761812</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.5444122324528045</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>350.2774927830222</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>4487023.912959279</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>4983287.220802533</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>2.1105996574722865</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>1.1105996574722865</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>69.1901970736</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.776435985751353</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>59.7634947847954</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>69.1901970736</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>72.30344696034051</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$153,A15,'Species'!$U$2:$U$153))</x:f>
-        <x:v>5002.689744286545</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.776435985751353</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>59.7634947847954</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>4135.04798196706</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>867.6417623194848</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.2098262864429312</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.20982628644293116</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>5132.175707328999</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.9486818341475063</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>88.85499241701632</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>5132.175707328999</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>147.98493314765884</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$153,A16,'Species'!$U$2:$U$153))</x:f>
-        <x:v>759484.6789511207</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.9486818341475063</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>88.85499241701632</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>456019.4335575136</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>303465.2453936071</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.6654655987491678</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.6654655987491678</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>2576.2280234887</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.1305602798319865</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>135.07042918475346</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>2576.2280234887</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>140.52327749846725</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$153,A17,'Species'!$U$2:$U$153))</x:f>
-        <x:v>362020.0054440304</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.1305602798319865</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>135.07042918475346</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>347972.2248104078</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>14047.780633622606</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0403704078429723</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.0403704078429723</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>4009.5189351211</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.662633183753656</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>459.867993212782</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>4009.5189351211</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>538.8715129485848</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$153,A18,'Species'!$U$2:$U$153))</x:f>
-        <x:v>2160615.534764706</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.662633183753656</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>459.867993212782</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>1843849.426442791</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>316766.10832191515</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.171796082575479</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.1717960825754789</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>67267.11349145763</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.4516693304762507</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>28.292370093963285</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>67267.11349145763</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>32.962928887001766</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$153,A19,'Species'!$U$2:$U$153))</x:f>
-        <x:v>2217321.078452795</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.4516693304762507</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>28.292370093963285</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>1903146.07005295</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>314175.00839984487</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.165081920585898</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.16508192058589796</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>1252.0868014387997</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>4.013540389561516</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>1031.6690206120743</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>1252.0868014387997</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>1038.088132257277</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$153,A20,'Species'!$U$2:$U$153))</x:f>
-        <x:v>1299776.4491295917</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>4.013540389561516</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>1031.6690206120743</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>1291739.1641616712</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>8037.28496792051</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0062220649422955</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.006222064942295565</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>2468.9442106813003</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>4.308735103275783</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>2035.7999683447206</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>2468.9442106813003</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>2303.093839271421</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$153,A21,'Species'!$U$2:$U$153))</x:f>
-        <x:v>5686210.201124945</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>4.308735103275783</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>2035.7999683447206</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>5026276.545949873</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>659933.6551750721</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.131296726143499</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.13129672614349894</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>157.2375056633</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.8999999999999995</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>794.3282347242805</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>157.2375056633</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$153,A22,'Species'!$U$2:$U$153))</x:f>
-        <x:v>124898.19030597826</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.8999999999999995</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>794.3282347242805</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>124898.19030597815</x:v>
       </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>1.1641532182693481e-10</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>9.320817342648294e-16</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G22">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O22">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0375bf381ba4448d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R864355777e1543ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12907,7 +11668,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -13006,7 +11767,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>498970402.0793729</x:v>
+        <x:v>413435716.0336292</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13020,7 +11781,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>498970402.07937294</x:v>
+        <x:v>456002816.85696054</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13034,7 +11795,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-85534686.0457437</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13048,7 +11809,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>5.960464477539063e-8</x:v>
+        <x:v>-42967585.22241235</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13059,9 +11820,9 @@
         <x:v>EEZ_923</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -13073,47 +11834,19 @@
         <x:v>EEZ_923</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_923</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_923</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re71c50b4dcf34a0e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb8aab0fefe049ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13160,7 +11893,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
